--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484323_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484323_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. FLOREN LARIO</t>
+          <t>L. PERALTA VISTUE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.2333</v>
+        <v>-0.4772</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0829</v>
+        <v>-0.2198</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3161</v>
+        <v>-0.2575</v>
       </c>
       <c r="G2" t="n">
-        <v>-3.6945</v>
+        <v>-1.5192</v>
       </c>
       <c r="H2" t="n">
-        <v>-3.0599</v>
+        <v>-0.9258</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6346000000000001</v>
+        <v>-0.5934</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.9768</v>
+        <v>-0.4908</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.3431</v>
+        <v>0.1023</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.7178</v>
+        <v>-1.0283</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.7168</v>
+        <v>-1.0281</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.001</v>
+        <v>-0.0002</v>
       </c>
       <c r="P2" t="n">
-        <v>1.7581</v>
+        <v>0.586</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.7581</v>
+        <v>0.586</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8166</v>
+        <v>-0.1534</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5051</v>
+        <v>-0.0062</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6885</v>
+        <v>-0.1472</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8865</v>
+        <v>0.6093</v>
       </c>
       <c r="W2" t="n">
-        <v>0.5545</v>
+        <v>0.2772</v>
       </c>
       <c r="X2" t="n">
         <v>0.3321</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. PERALTA VISTUE</t>
+          <t>D. FLOREN LARIO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.5511</v>
+        <v>-1.1428</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.3209</v>
+        <v>-0.9084</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2302</v>
+        <v>-0.2344</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.5192</v>
+        <v>-3.6945</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.9258</v>
+        <v>-3.0599</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5934</v>
+        <v>-0.6346000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.4908</v>
+        <v>-1.9768</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1023</v>
+        <v>-1.3431</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.0283</v>
+        <v>-1.7178</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.0281</v>
+        <v>-1.7168</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0002</v>
+        <v>-0.001</v>
       </c>
       <c r="P3" t="n">
-        <v>0.586</v>
+        <v>1.7581</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.586</v>
+        <v>1.7581</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2273</v>
+        <v>-0.0929</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1073</v>
+        <v>0.5139</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.12</v>
+        <v>-0.6068</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6093</v>
+        <v>0.8865</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2772</v>
+        <v>0.5545</v>
       </c>
       <c r="X3" t="n">
         <v>0.3321</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. VIDAL RAMOS</t>
+          <t>J. CASTELLO LOGROÑO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.8869</v>
+        <v>-2.2456</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.1169</v>
+        <v>1.3558</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.77</v>
+        <v>-3.6014</v>
       </c>
       <c r="G5" t="n">
-        <v>-4.0142</v>
+        <v>-3.1137</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.8397</v>
+        <v>-1.5349</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.1745</v>
+        <v>-1.5788</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.6081</v>
+        <v>-0.1821</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.6486</v>
+        <v>0.4515</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0405</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.4061</v>
+        <v>-2.9316</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.1911</v>
+        <v>-1.9864</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.215</v>
+        <v>-0.9451000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1721</v>
+        <v>1.3674</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1488</v>
+        <v>1.3674</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9552</v>
+        <v>-0.7766</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4679</v>
+        <v>0.0421</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4873</v>
+        <v>-0.8186</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.4959</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. CASTELLO LOGROÑO</t>
+          <t>F. VIDAL RAMOS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.8062</v>
+        <v>-2.8978</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9314</v>
+        <v>-1.5014</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.7376</v>
+        <v>-1.3964</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.1137</v>
+        <v>-4.0142</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.5349</v>
+        <v>-2.8397</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.5788</v>
+        <v>-1.1745</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1821</v>
+        <v>-0.6081</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4515</v>
+        <v>-0.6486</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0.0405</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.9316</v>
+        <v>-3.4061</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.9864</v>
+        <v>-2.1911</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9451000000000001</v>
+        <v>-1.215</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3674</v>
+        <v>2.1488</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.3371</v>
+        <v>-0.0557</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3823</v>
+        <v>0.0834</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.9548</v>
+        <v>-0.1391</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.8494</v>
+        <v>-3.2422</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7825</v>
+        <v>-0.257</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.0668</v>
+        <v>-2.9851</v>
       </c>
       <c r="G7" t="n">
         <v>-3.4369</v>
@@ -1000,13 +1000,13 @@
         <v>0.586</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6664</v>
+        <v>-0.0592</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3494</v>
+        <v>0.1761</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.317</v>
+        <v>-0.2353</v>
       </c>
       <c r="V7" t="n">
         <v>-0.3321</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. KIRIS</t>
+          <t>R. BORGES PINO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.0402</v>
+        <v>-4.0381</v>
       </c>
       <c r="E8" t="n">
-        <v>1.2404</v>
+        <v>-0.9519</v>
       </c>
       <c r="F8" t="n">
-        <v>-5.2806</v>
+        <v>-3.0862</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.8059</v>
+        <v>-3.8436</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0399</v>
+        <v>-3.384</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.8458</v>
+        <v>-0.4595</v>
       </c>
       <c r="J8" t="n">
-        <v>3.3769</v>
+        <v>0.5810999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>2.8498</v>
+        <v>-0.7138</v>
       </c>
       <c r="L8" t="n">
-        <v>0.527</v>
+        <v>1.2949</v>
       </c>
       <c r="M8" t="n">
-        <v>-6.1828</v>
+        <v>-4.4247</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.8099</v>
+        <v>-2.6703</v>
       </c>
       <c r="O8" t="n">
-        <v>-3.3729</v>
+        <v>-1.7544</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.7581</v>
+        <v>1.3674</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.9069</v>
+        <v>-0.9767</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1488</v>
+        <v>2.3441</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4176</v>
+        <v>-0.9526</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0576</v>
+        <v>-0.5563</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.36</v>
+        <v>-0.3963</v>
       </c>
       <c r="V8" t="n">
-        <v>0.9414</v>
+        <v>-0.6093</v>
       </c>
       <c r="W8" t="n">
-        <v>1.8279</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.8865</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. BORGES PINO</t>
+          <t>M. KIRIS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.5497</v>
+        <v>-4.102</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.518</v>
+        <v>1.2603</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.0317</v>
+        <v>-5.3623</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.8436</v>
+        <v>-2.8059</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.384</v>
+        <v>0.0399</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4595</v>
+        <v>-2.8458</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5810999999999999</v>
+        <v>3.3769</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7138</v>
+        <v>2.8498</v>
       </c>
       <c r="L9" t="n">
-        <v>1.2949</v>
+        <v>0.527</v>
       </c>
       <c r="M9" t="n">
-        <v>-4.4247</v>
+        <v>-6.1828</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.6703</v>
+        <v>-2.8099</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.7544</v>
+        <v>-3.3729</v>
       </c>
       <c r="P9" t="n">
-        <v>1.3674</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9767</v>
+        <v>-3.9069</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3441</v>
+        <v>2.1488</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.4642</v>
+        <v>-0.4794</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1224</v>
+        <v>-0.0377</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3419</v>
+        <v>-0.4417</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6093</v>
+        <v>0.9414</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.8279</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6093</v>
+        <v>-0.8865</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.3418</v>
+        <v>-5.6667</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.8046</v>
+        <v>-4.2385</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5371</v>
+        <v>-1.4282</v>
       </c>
       <c r="G10" t="n">
         <v>-5.358</v>
@@ -1234,13 +1234,13 @@
         <v>1.9534</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9838</v>
+        <v>-0.3088</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9546</v>
+        <v>-0.3885</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0292</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.0142</v>
+        <v>-6.5524</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0813</v>
+        <v>-1.0008</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.9329</v>
+        <v>-5.5516</v>
       </c>
       <c r="G11" t="n">
         <v>-0.5847</v>
@@ -1312,13 +1312,13 @@
         <v>1.7581</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4212</v>
+        <v>-0.9595</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0576</v>
+        <v>0.0229</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.3636</v>
+        <v>-0.9824000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>-1.8828</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-33.1007</v>
+        <v>-32.1927</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.369499999999999</v>
+        <v>-6.4617</v>
       </c>
       <c r="F12" t="n">
-        <v>-25.7309</v>
+        <v>-25.731</v>
       </c>
       <c r="G12" t="n">
         <v>-28.3707</v>
@@ -1366,7 +1366,7 @@
         <v>2.6172</v>
       </c>
       <c r="K12" t="n">
-        <v>5.310500000000001</v>
+        <v>5.3105</v>
       </c>
       <c r="L12" t="n">
         <v>-2.6934</v>
@@ -1390,10 +1390,10 @@
         <v>14.6507</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.7458</v>
+        <v>-3.8381</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0582</v>
+        <v>-0.1502999999999999</v>
       </c>
       <c r="U12" t="n">
         <v>-3.6877</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.577999999999999</v>
+        <v>10.3361</v>
       </c>
       <c r="E13" t="n">
-        <v>6.8237</v>
+        <v>7.6326</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7543</v>
+        <v>2.7035</v>
       </c>
       <c r="G13" t="n">
         <v>8.4457</v>
@@ -1468,13 +1468,13 @@
         <v>1.7581</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8557</v>
+        <v>0.9024</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3548</v>
+        <v>0.4541</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5009</v>
+        <v>0.4483</v>
       </c>
       <c r="V13" t="n">
         <v>2.16</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.7104</v>
+        <v>5.8068</v>
       </c>
       <c r="E14" t="n">
-        <v>5.6774</v>
+        <v>4.2617</v>
       </c>
       <c r="F14" t="n">
-        <v>1.033</v>
+        <v>1.5451</v>
       </c>
       <c r="G14" t="n">
         <v>4.861</v>
@@ -1546,13 +1546,13 @@
         <v>1.5627</v>
       </c>
       <c r="S14" t="n">
-        <v>1.9628</v>
+        <v>1.0593</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2727</v>
+        <v>0.8571</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3099</v>
+        <v>0.2021</v>
       </c>
       <c r="V14" t="n">
         <v>0.2772</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.1735</v>
+        <v>4.0923</v>
       </c>
       <c r="E15" t="n">
-        <v>4.6775</v>
+        <v>3.7675</v>
       </c>
       <c r="F15" t="n">
-        <v>1.496</v>
+        <v>0.3248</v>
       </c>
       <c r="G15" t="n">
         <v>4.4918</v>
@@ -1624,13 +1624,13 @@
         <v>0.9767</v>
       </c>
       <c r="S15" t="n">
-        <v>3.877</v>
+        <v>1.7959</v>
       </c>
       <c r="T15" t="n">
-        <v>1.296</v>
+        <v>0.386</v>
       </c>
       <c r="U15" t="n">
-        <v>2.581</v>
+        <v>1.4099</v>
       </c>
       <c r="V15" t="n">
         <v>-1.2186</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. SALO BLAYA</t>
+          <t>I. JUNCADELLA ENFEDAQUE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,40 +1657,40 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.8042</v>
+        <v>4.0799</v>
       </c>
       <c r="E16" t="n">
-        <v>2.7991</v>
+        <v>2.648</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0051</v>
+        <v>1.4319</v>
       </c>
       <c r="G16" t="n">
-        <v>1.7222</v>
+        <v>-0.1188</v>
       </c>
       <c r="H16" t="n">
-        <v>1.0075</v>
+        <v>-1.6168</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7148</v>
+        <v>1.498</v>
       </c>
       <c r="J16" t="n">
-        <v>2.6303</v>
+        <v>0.4549</v>
       </c>
       <c r="K16" t="n">
-        <v>1.7805</v>
+        <v>-0.7739</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8498</v>
+        <v>1.2288</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9081</v>
+        <v>-0.5737</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7731</v>
+        <v>-0.8429</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.135</v>
+        <v>0.2692</v>
       </c>
       <c r="P16" t="n">
         <v>0.586</v>
@@ -1702,19 +1702,19 @@
         <v>1.5627</v>
       </c>
       <c r="S16" t="n">
-        <v>1.828</v>
+        <v>0.5661</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4776</v>
+        <v>0.1232</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3504</v>
+        <v>0.4429</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.3321</v>
+        <v>3.0466</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.3321</v>
+        <v>3.0466</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. JUNCADELLA ENFEDAQUE</t>
+          <t>A. SALO BLAYA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,40 +1735,40 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.5476</v>
+        <v>3.0017</v>
       </c>
       <c r="E17" t="n">
-        <v>1.738</v>
+        <v>1.8891</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8096</v>
+        <v>1.1126</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1188</v>
+        <v>1.7222</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.6168</v>
+        <v>1.0075</v>
       </c>
       <c r="I17" t="n">
-        <v>1.498</v>
+        <v>0.7148</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4549</v>
+        <v>2.6303</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.7739</v>
+        <v>1.7805</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2288</v>
+        <v>0.8498</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5737</v>
+        <v>-0.9081</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8429</v>
+        <v>-0.7731</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2692</v>
+        <v>-0.135</v>
       </c>
       <c r="P17" t="n">
         <v>0.586</v>
@@ -1780,19 +1780,19 @@
         <v>1.5627</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9663</v>
+        <v>1.0255</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7868000000000001</v>
+        <v>0.5676</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1795</v>
+        <v>0.458</v>
       </c>
       <c r="V17" t="n">
-        <v>3.0466</v>
+        <v>-0.3321</v>
       </c>
       <c r="W17" t="n">
-        <v>3.0466</v>
+        <v>-0.3321</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. KEITA</t>
+          <t>P. MONÉS RIERA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.398</v>
+        <v>2.4267</v>
       </c>
       <c r="E18" t="n">
-        <v>2.2587</v>
+        <v>3.8167</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1394</v>
+        <v>-1.39</v>
       </c>
       <c r="G18" t="n">
-        <v>3.1393</v>
+        <v>2.5854</v>
       </c>
       <c r="H18" t="n">
-        <v>2.2633</v>
+        <v>-2.1765</v>
       </c>
       <c r="I18" t="n">
-        <v>0.876</v>
+        <v>4.7619</v>
       </c>
       <c r="J18" t="n">
-        <v>2.8245</v>
+        <v>3.7678</v>
       </c>
       <c r="K18" t="n">
-        <v>2.6222</v>
+        <v>-0.5897</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2023</v>
+        <v>4.3575</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3148</v>
+        <v>-1.1824</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3589</v>
+        <v>-1.5868</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6737</v>
+        <v>0.4045</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.7814</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="S18" t="n">
-        <v>1.0867</v>
+        <v>0.2786</v>
       </c>
       <c r="T18" t="n">
-        <v>0.743</v>
+        <v>0.0489</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3437</v>
+        <v>0.2297</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.8279</v>
+        <v>-1.2186</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.4959</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>H. LOUASSA</t>
+          <t>A. KEITA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.9513</v>
+        <v>2.394</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1787</v>
+        <v>2.2587</v>
       </c>
       <c r="F19" t="n">
-        <v>2.13</v>
+        <v>0.1353</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2068</v>
+        <v>3.1393</v>
       </c>
       <c r="H19" t="n">
-        <v>2.0044</v>
+        <v>2.2633</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.2112</v>
+        <v>0.876</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0029</v>
+        <v>2.8245</v>
       </c>
       <c r="K19" t="n">
-        <v>1.9442</v>
+        <v>2.6222</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.9414</v>
+        <v>0.2023</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2097</v>
+        <v>0.3148</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0601</v>
+        <v>-0.3589</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2698</v>
+        <v>0.6737</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1721</v>
+        <v>0.9767</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3423</v>
+        <v>1.0826</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1816</v>
+        <v>0.743</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1607</v>
+        <v>0.3397</v>
       </c>
       <c r="V19" t="n">
-        <v>1.3283</v>
+        <v>-1.8279</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="X19" t="n">
-        <v>1.3283</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. MONÉS RIERA</t>
+          <t>H. LOUASSA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.8912</v>
+        <v>2.3169</v>
       </c>
       <c r="E20" t="n">
-        <v>3.7156</v>
+        <v>0.0235</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.8244</v>
+        <v>2.2934</v>
       </c>
       <c r="G20" t="n">
-        <v>2.5854</v>
+        <v>-0.2068</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.1765</v>
+        <v>2.0044</v>
       </c>
       <c r="I20" t="n">
-        <v>4.7619</v>
+        <v>-2.2112</v>
       </c>
       <c r="J20" t="n">
-        <v>3.7678</v>
+        <v>0.0029</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5897</v>
+        <v>1.9442</v>
       </c>
       <c r="L20" t="n">
-        <v>4.3575</v>
+        <v>-1.9414</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1824</v>
+        <v>-0.2097</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.5868</v>
+        <v>0.0601</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4045</v>
+        <v>-0.2698</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7814</v>
+        <v>1.1721</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7814</v>
+        <v>1.1721</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2569</v>
+        <v>0.0234</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0522</v>
+        <v>0.0207</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2047</v>
+        <v>0.0027</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2186</v>
+        <v>1.3283</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2186</v>
+        <v>1.3283</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2999</v>
+        <v>1.4758</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1893</v>
+        <v>0.796</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1106</v>
+        <v>0.6798999999999999</v>
       </c>
       <c r="G21" t="n">
         <v>2.6259</v>
@@ -2092,13 +2092,13 @@
         <v>1.5627</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9586</v>
+        <v>0.2174</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4842</v>
+        <v>0.1225</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4744</v>
+        <v>0.0949</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.2534</v>
+        <v>-0.1333</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.9694</v>
+        <v>-1.3627</v>
       </c>
       <c r="F22" t="n">
-        <v>0.716</v>
+        <v>1.2294</v>
       </c>
       <c r="G22" t="n">
         <v>0.8249</v>
@@ -2170,13 +2170,13 @@
         <v>0.7814</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.629</v>
+        <v>0.4911</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2421</v>
+        <v>0.3646</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3869</v>
+        <v>0.1265</v>
       </c>
       <c r="V22" t="n">
         <v>-0.2772</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>33.1007</v>
+        <v>35.7969</v>
       </c>
       <c r="E23" t="n">
-        <v>25.7312</v>
+        <v>25.7311</v>
       </c>
       <c r="F23" t="n">
-        <v>7.3696</v>
+        <v>10.0659</v>
       </c>
       <c r="G23" t="n">
         <v>28.3706</v>
@@ -2236,7 +2236,7 @@
         <v>-5.3106</v>
       </c>
       <c r="O23" t="n">
-        <v>2.693499999999999</v>
+        <v>2.6935</v>
       </c>
       <c r="P23" t="n">
         <v>-1.9535</v>
@@ -2248,19 +2248,19 @@
         <v>12.6972</v>
       </c>
       <c r="S23" t="n">
-        <v>4.745700000000001</v>
+        <v>7.4423</v>
       </c>
       <c r="T23" t="n">
-        <v>3.6876</v>
+        <v>3.6877</v>
       </c>
       <c r="U23" t="n">
-        <v>1.0581</v>
+        <v>3.7547</v>
       </c>
       <c r="V23" t="n">
         <v>1.9377</v>
       </c>
       <c r="W23" t="n">
-        <v>5.706200000000001</v>
+        <v>5.7062</v>
       </c>
       <c r="X23" t="n">
         <v>-3.7685</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484323_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484323_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,11 +549,16 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>L. PERALTA VISTUE</t>
+          <t>P. CABAÑERO PUERTAS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +570,78 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.4772</v>
+        <v>2.4489</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.2198</v>
+        <v>2.4489</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2575</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.5192</v>
+        <v>2.4489</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.9258</v>
+        <v>1.8419</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5934</v>
+        <v>0.607</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.4908</v>
+        <v>2.4489</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1023</v>
+        <v>1.8419</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.5931999999999999</v>
+        <v>0.607</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.0283</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.0281</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.0002</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1534</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0062</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1472</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.3321</v>
+        <v>0</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484323_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. FLOREN LARIO</t>
+          <t>J. CASTELLO LOGROÑO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +653,78 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.1428</v>
+        <v>0.307</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.9084</v>
+        <v>0.307</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2344</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-3.6945</v>
+        <v>0.307</v>
       </c>
       <c r="H3" t="n">
-        <v>-3.0599</v>
+        <v>0.307</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6346000000000001</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.9768</v>
+        <v>0.307</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.3431</v>
+        <v>0.307</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.7178</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.7168</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.7581</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7581</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0929</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5139</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6068</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3321</v>
+        <v>0</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484323_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. CASADO FAJO</t>
+          <t>L. PERALTA VISTUE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +736,78 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.8279</v>
+        <v>-0.4772</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>-0.2198</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.8279</v>
+        <v>-0.2575</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>-1.5192</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>-0.9258</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>-0.5934</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>-0.4908</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>0.1023</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>-1.0283</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-1.0281</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-0.0002</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.586</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>0.586</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-0.1534</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>-0.0062</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>-0.1472</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.8279</v>
+        <v>0.6093</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.8279</v>
+        <v>0.3321</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484323_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. CASTELLO LOGROÑO</t>
+          <t>D. FLOREN LARIO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +819,78 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.2456</v>
+        <v>-1.1428</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3558</v>
+        <v>-0.9084</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.6014</v>
+        <v>-0.2344</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.1137</v>
+        <v>-3.6945</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.5349</v>
+        <v>-3.0599</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.5788</v>
+        <v>-0.6346000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1821</v>
+        <v>-1.9768</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4515</v>
+        <v>-1.3431</v>
       </c>
       <c r="L5" t="n">
         <v>-0.6336000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.9316</v>
+        <v>-1.7178</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.9864</v>
+        <v>-1.7168</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9451000000000001</v>
+        <v>-0.001</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3674</v>
+        <v>1.7581</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3674</v>
+        <v>1.7581</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7766</v>
+        <v>-0.0929</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0421</v>
+        <v>0.5139</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8186</v>
+        <v>-0.6068</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2772</v>
+        <v>0.8865</v>
       </c>
       <c r="W5" t="n">
-        <v>1.4959</v>
+        <v>0.5545</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2186</v>
+        <v>0.3321</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484323_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. VIDAL RAMOS</t>
+          <t>M. CASADO FAJO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.8978</v>
+        <v>-1.8279</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.5014</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3964</v>
+        <v>-1.8279</v>
       </c>
       <c r="G6" t="n">
-        <v>-4.0142</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.8397</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.1745</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6081</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6486</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0405</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.4061</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.1911</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.215</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1488</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0557</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0834</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1391</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.8279</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.8279</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484323_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. GEORGIOU</t>
+          <t>J. CASTELLO LOGRONO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.2422</v>
+        <v>-2.5526</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.257</v>
+        <v>1.0488</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.9851</v>
+        <v>-3.6014</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.4369</v>
+        <v>-3.4207</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0289</v>
+        <v>-1.8419</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.4658</v>
+        <v>-1.5788</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.7104</v>
+        <v>-0.4891</v>
       </c>
       <c r="K7" t="n">
-        <v>1.9455</v>
+        <v>0.1445</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.6559</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.7265</v>
+        <v>-2.9316</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.9166</v>
+        <v>-1.9864</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8099</v>
+        <v>-0.9451000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>0.586</v>
+        <v>1.3674</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.586</v>
+        <v>1.3674</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0592</v>
+        <v>-0.7766</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1761</v>
+        <v>0.0421</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2353</v>
+        <v>-0.8186</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3321</v>
+        <v>0.2772</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2772</v>
+        <v>1.4959</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6093</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484323_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. BORGES PINO</t>
+          <t>F. VIDAL RAMOS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.0381</v>
+        <v>-2.8978</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9519</v>
+        <v>-1.5014</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.0862</v>
+        <v>-1.3964</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.8436</v>
+        <v>-4.0142</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.384</v>
+        <v>-2.8397</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4595</v>
+        <v>-1.1745</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5810999999999999</v>
+        <v>-0.6081</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7138</v>
+        <v>-0.6486</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2949</v>
+        <v>0.0405</v>
       </c>
       <c r="M8" t="n">
-        <v>-4.4247</v>
+        <v>-3.4061</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.6703</v>
+        <v>-2.1911</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.7544</v>
+        <v>-1.215</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3441</v>
+        <v>2.1488</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9526</v>
+        <v>-0.0557</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5563</v>
+        <v>0.0834</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3963</v>
+        <v>-0.1391</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484323_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. KIRIS</t>
+          <t>G. GEORGIOU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.102</v>
+        <v>-3.2422</v>
       </c>
       <c r="E9" t="n">
-        <v>1.2603</v>
+        <v>-0.257</v>
       </c>
       <c r="F9" t="n">
-        <v>-5.3623</v>
+        <v>-2.9851</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.8059</v>
+        <v>-3.4369</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0399</v>
+        <v>0.0289</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.8458</v>
+        <v>-3.4658</v>
       </c>
       <c r="J9" t="n">
-        <v>3.3769</v>
+        <v>-0.7104</v>
       </c>
       <c r="K9" t="n">
-        <v>2.8498</v>
+        <v>1.9455</v>
       </c>
       <c r="L9" t="n">
-        <v>0.527</v>
+        <v>-2.6559</v>
       </c>
       <c r="M9" t="n">
-        <v>-6.1828</v>
+        <v>-2.7265</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.8099</v>
+        <v>-1.9166</v>
       </c>
       <c r="O9" t="n">
-        <v>-3.3729</v>
+        <v>-0.8099</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.7581</v>
+        <v>0.586</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.9069</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1488</v>
+        <v>0.586</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4794</v>
+        <v>-0.0592</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0377</v>
+        <v>0.1761</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4417</v>
+        <v>-0.2353</v>
       </c>
       <c r="V9" t="n">
-        <v>0.9414</v>
+        <v>-0.3321</v>
       </c>
       <c r="W9" t="n">
-        <v>1.8279</v>
+        <v>0.2772</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.8865</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484323_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. RAMOS SAINZ</t>
+          <t>R. BORGES PINO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.6667</v>
+        <v>-4.0381</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.2385</v>
+        <v>-0.9519</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4282</v>
+        <v>-3.0862</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.358</v>
+        <v>-3.8436</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.3927</v>
+        <v>-3.384</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.9652</v>
+        <v>-0.4595</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.8966</v>
+        <v>0.5810999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0447</v>
+        <v>-0.7138</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.9414</v>
+        <v>1.2949</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.4613</v>
+        <v>-4.4247</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.4375</v>
+        <v>-2.6703</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.0239</v>
+        <v>-1.7544</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.3674</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9534</v>
+        <v>2.3441</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3088</v>
+        <v>-0.9526</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3885</v>
+        <v>-0.5563</v>
       </c>
       <c r="U10" t="n">
-        <v>0.07969999999999999</v>
+        <v>-0.3963</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484323_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. CABAÑERO PUERTAS</t>
+          <t>M. KIRIS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.5524</v>
+        <v>-4.102</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0008</v>
+        <v>1.2603</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.5516</v>
+        <v>-5.3623</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.5847</v>
+        <v>-2.8059</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4623</v>
+        <v>0.0399</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1224</v>
+        <v>-2.8458</v>
       </c>
       <c r="J11" t="n">
-        <v>4.524</v>
+        <v>3.3769</v>
       </c>
       <c r="K11" t="n">
-        <v>2.6222</v>
+        <v>2.8498</v>
       </c>
       <c r="L11" t="n">
-        <v>1.9019</v>
+        <v>0.527</v>
       </c>
       <c r="M11" t="n">
-        <v>-5.1087</v>
+        <v>-6.1828</v>
       </c>
       <c r="N11" t="n">
-        <v>-3.0844</v>
+        <v>-2.8099</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.0243</v>
+        <v>-3.3729</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.1255</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.8836</v>
+        <v>-3.9069</v>
       </c>
       <c r="R11" t="n">
-        <v>1.7581</v>
+        <v>2.1488</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9595</v>
+        <v>-0.4794</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0229</v>
+        <v>-0.0377</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.9824000000000001</v>
+        <v>-0.4417</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.8828</v>
+        <v>0.9414</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.6642</v>
+        <v>1.8279</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2186</v>
+        <v>-0.8865</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484323_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>P. RAMOS SAINZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,229 +1400,240 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-32.1927</v>
+        <v>-5.6667</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.4617</v>
+        <v>-4.2385</v>
       </c>
       <c r="F12" t="n">
-        <v>-25.731</v>
+        <v>-1.4282</v>
       </c>
       <c r="G12" t="n">
-        <v>-28.3707</v>
+        <v>-5.358</v>
       </c>
       <c r="H12" t="n">
-        <v>-13.5305</v>
+        <v>-1.3927</v>
       </c>
       <c r="I12" t="n">
-        <v>-14.84</v>
+        <v>-3.9652</v>
       </c>
       <c r="J12" t="n">
-        <v>2.6172</v>
+        <v>-1.8966</v>
       </c>
       <c r="K12" t="n">
-        <v>5.3105</v>
+        <v>0.0447</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.6934</v>
+        <v>-1.9414</v>
       </c>
       <c r="M12" t="n">
-        <v>-30.9878</v>
+        <v>-3.4613</v>
       </c>
       <c r="N12" t="n">
-        <v>-18.8411</v>
+        <v>-1.4375</v>
       </c>
       <c r="O12" t="n">
-        <v>-12.1467</v>
+        <v>-2.0239</v>
       </c>
       <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R12" t="n">
         <v>1.9534</v>
       </c>
-      <c r="Q12" t="n">
-        <v>-12.6973</v>
-      </c>
-      <c r="R12" t="n">
-        <v>14.6507</v>
-      </c>
       <c r="S12" t="n">
-        <v>-3.8381</v>
+        <v>-0.3088</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1502999999999999</v>
+        <v>-0.3885</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.6877</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.9377</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>3.7685</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-5.706</v>
+        <v>0</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484323_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. BATALLER LOPEZ</t>
+          <t>P. CABANERO PUERTAS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CB NAVÀS VISCOLA</t>
+          <t>FRIVALCA LA MUELA</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.3361</v>
+        <v>-9.001300000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>7.6326</v>
+        <v>-3.4497</v>
       </c>
       <c r="F13" t="n">
-        <v>2.7035</v>
+        <v>-5.5516</v>
       </c>
       <c r="G13" t="n">
-        <v>8.4457</v>
+        <v>-3.0336</v>
       </c>
       <c r="H13" t="n">
-        <v>2.2004</v>
+        <v>-2.3042</v>
       </c>
       <c r="I13" t="n">
-        <v>6.2453</v>
+        <v>-0.7294</v>
       </c>
       <c r="J13" t="n">
-        <v>7.6714</v>
+        <v>2.0751</v>
       </c>
       <c r="K13" t="n">
-        <v>1.9647</v>
+        <v>0.7802</v>
       </c>
       <c r="L13" t="n">
-        <v>5.7067</v>
+        <v>1.2949</v>
       </c>
       <c r="M13" t="n">
-        <v>0.7743</v>
+        <v>-5.1087</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2357</v>
+        <v>-3.0844</v>
       </c>
       <c r="O13" t="n">
-        <v>0.5387</v>
+        <v>-2.0243</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.1721</v>
+        <v>-3.1255</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.9301</v>
+        <v>-4.8836</v>
       </c>
       <c r="R13" t="n">
         <v>1.7581</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9024</v>
+        <v>-0.9595</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4541</v>
+        <v>0.0229</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4483</v>
+        <v>-0.9824000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>2.16</v>
+        <v>-1.8828</v>
       </c>
       <c r="W13" t="n">
-        <v>2.4373</v>
+        <v>-0.6642</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484323_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. ZHURAVLOV</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CB NAVÀS VISCOLA</t>
+          <t>FRIVALCA LA MUELA</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.8068</v>
+        <v>-32.1927</v>
       </c>
       <c r="E14" t="n">
-        <v>4.2617</v>
+        <v>-6.4617</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5451</v>
+        <v>-25.731</v>
       </c>
       <c r="G14" t="n">
-        <v>4.861</v>
+        <v>-28.3707</v>
       </c>
       <c r="H14" t="n">
-        <v>3.998</v>
+        <v>-13.5305</v>
       </c>
       <c r="I14" t="n">
-        <v>0.863</v>
+        <v>-14.84</v>
       </c>
       <c r="J14" t="n">
-        <v>5.0808</v>
+        <v>2.6172</v>
       </c>
       <c r="K14" t="n">
-        <v>4.2172</v>
+        <v>5.3104</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8636</v>
+        <v>-2.693399999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.2198</v>
+        <v>-30.9878</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2192</v>
+        <v>-18.8411</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-12.1467</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.3907</v>
+        <v>1.9534</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9534</v>
+        <v>-12.6973</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5627</v>
+        <v>14.6507</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0593</v>
+        <v>-3.8381</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8571</v>
+        <v>-0.1503</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2021</v>
+        <v>-3.6877</v>
       </c>
       <c r="V14" t="n">
-        <v>0.2772</v>
+        <v>-1.9377</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2772</v>
+        <v>3.7685</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
-      </c>
+        <v>-5.706</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. FALL</t>
+          <t>M. BATALLER LOPEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.0923</v>
+        <v>10.3361</v>
       </c>
       <c r="E15" t="n">
-        <v>3.7675</v>
+        <v>7.6326</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3248</v>
+        <v>2.7035</v>
       </c>
       <c r="G15" t="n">
-        <v>4.4918</v>
+        <v>8.4457</v>
       </c>
       <c r="H15" t="n">
-        <v>3.6693</v>
+        <v>2.2004</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8225</v>
+        <v>6.2453</v>
       </c>
       <c r="J15" t="n">
-        <v>4.7256</v>
+        <v>7.6714</v>
       </c>
       <c r="K15" t="n">
-        <v>4.4423</v>
+        <v>1.9647</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2833</v>
+        <v>5.7067</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2338</v>
+        <v>0.7743</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7731</v>
+        <v>0.2357</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5393</v>
+        <v>0.5387</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.9767</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9534</v>
+        <v>-2.9301</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9767</v>
+        <v>1.7581</v>
       </c>
       <c r="S15" t="n">
-        <v>1.7959</v>
+        <v>0.9024</v>
       </c>
       <c r="T15" t="n">
-        <v>0.386</v>
+        <v>0.4541</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4099</v>
+        <v>0.4483</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.2186</v>
+        <v>2.16</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6093</v>
+        <v>2.4373</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.8279</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484323_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. JUNCADELLA ENFEDAQUE</t>
+          <t>D. ZHURAVLOV</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.0799</v>
+        <v>5.8068</v>
       </c>
       <c r="E16" t="n">
-        <v>2.648</v>
+        <v>4.2617</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4319</v>
+        <v>1.5451</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1188</v>
+        <v>4.861</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.6168</v>
+        <v>3.998</v>
       </c>
       <c r="I16" t="n">
-        <v>1.498</v>
+        <v>0.863</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4549</v>
+        <v>5.0808</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.7739</v>
+        <v>4.2172</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2288</v>
+        <v>0.8636</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5737</v>
+        <v>-0.2198</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8429</v>
+        <v>-0.2192</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2692</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>0.586</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R16" t="n">
         <v>1.5627</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5661</v>
+        <v>1.0593</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1232</v>
+        <v>0.8571</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4429</v>
+        <v>0.2021</v>
       </c>
       <c r="V16" t="n">
-        <v>3.0466</v>
+        <v>0.2772</v>
       </c>
       <c r="W16" t="n">
-        <v>3.0466</v>
+        <v>0.2772</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484323_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. SALO BLAYA</t>
+          <t>A. FALL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.0017</v>
+        <v>4.0923</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8891</v>
+        <v>3.7675</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1126</v>
+        <v>0.3248</v>
       </c>
       <c r="G17" t="n">
-        <v>1.7222</v>
+        <v>4.4918</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0075</v>
+        <v>3.6693</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7148</v>
+        <v>0.8225</v>
       </c>
       <c r="J17" t="n">
-        <v>2.6303</v>
+        <v>4.7256</v>
       </c>
       <c r="K17" t="n">
-        <v>1.7805</v>
+        <v>4.4423</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8498</v>
+        <v>0.2833</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9081</v>
+        <v>-0.2338</v>
       </c>
       <c r="N17" t="n">
         <v>-0.7731</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.135</v>
+        <v>0.5393</v>
       </c>
       <c r="P17" t="n">
-        <v>0.586</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5627</v>
+        <v>0.9767</v>
       </c>
       <c r="S17" t="n">
-        <v>1.0255</v>
+        <v>1.7959</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5676</v>
+        <v>0.386</v>
       </c>
       <c r="U17" t="n">
-        <v>0.458</v>
+        <v>1.4099</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3321</v>
+        <v>-1.2186</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3321</v>
+        <v>0.6093</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.8279</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484323_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. MONÉS RIERA</t>
+          <t>I. JUNCADELLA ENFEDAQUE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.4267</v>
+        <v>4.0799</v>
       </c>
       <c r="E18" t="n">
-        <v>3.8167</v>
+        <v>2.648</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.39</v>
+        <v>1.4319</v>
       </c>
       <c r="G18" t="n">
-        <v>2.5854</v>
+        <v>-0.1188</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.1765</v>
+        <v>-1.6168</v>
       </c>
       <c r="I18" t="n">
-        <v>4.7619</v>
+        <v>1.498</v>
       </c>
       <c r="J18" t="n">
-        <v>3.7678</v>
+        <v>0.4549</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5897</v>
+        <v>-0.7739</v>
       </c>
       <c r="L18" t="n">
-        <v>4.3575</v>
+        <v>1.2288</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.1824</v>
+        <v>-0.5737</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.5868</v>
+        <v>-0.8429</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4045</v>
+        <v>0.2692</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7814</v>
+        <v>0.586</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7814</v>
+        <v>1.5627</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2786</v>
+        <v>0.5661</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0489</v>
+        <v>0.1232</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2297</v>
+        <v>0.4429</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2186</v>
+        <v>3.0466</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>3.0466</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484323_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. KEITA</t>
+          <t>A. SALO BLAYA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.394</v>
+        <v>3.0017</v>
       </c>
       <c r="E19" t="n">
-        <v>2.2587</v>
+        <v>1.8891</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1353</v>
+        <v>1.1126</v>
       </c>
       <c r="G19" t="n">
-        <v>3.1393</v>
+        <v>1.7222</v>
       </c>
       <c r="H19" t="n">
-        <v>2.2633</v>
+        <v>1.0075</v>
       </c>
       <c r="I19" t="n">
-        <v>0.876</v>
+        <v>0.7148</v>
       </c>
       <c r="J19" t="n">
-        <v>2.8245</v>
+        <v>2.6303</v>
       </c>
       <c r="K19" t="n">
-        <v>2.6222</v>
+        <v>1.7805</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2023</v>
+        <v>0.8498</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3148</v>
+        <v>-0.9081</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3589</v>
+        <v>-0.7731</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6737</v>
+        <v>-0.135</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.586</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9767</v>
+        <v>1.5627</v>
       </c>
       <c r="S19" t="n">
-        <v>1.0826</v>
+        <v>1.0255</v>
       </c>
       <c r="T19" t="n">
-        <v>0.743</v>
+        <v>0.5676</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3397</v>
+        <v>0.458</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.8279</v>
+        <v>-0.3321</v>
       </c>
       <c r="W19" t="n">
         <v>-0.3321</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484323_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>H. LOUASSA</t>
+          <t>A. KEITA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.3169</v>
+        <v>2.394</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0235</v>
+        <v>2.2587</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2934</v>
+        <v>0.1353</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2068</v>
+        <v>3.1393</v>
       </c>
       <c r="H20" t="n">
-        <v>2.0044</v>
+        <v>2.2633</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.2112</v>
+        <v>0.876</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0029</v>
+        <v>2.8245</v>
       </c>
       <c r="K20" t="n">
-        <v>1.9442</v>
+        <v>2.6222</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.9414</v>
+        <v>0.2023</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2097</v>
+        <v>0.3148</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0601</v>
+        <v>-0.3589</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2698</v>
+        <v>0.6737</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1721</v>
+        <v>0.9767</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0234</v>
+        <v>1.0826</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0207</v>
+        <v>0.743</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0027</v>
+        <v>0.3397</v>
       </c>
       <c r="V20" t="n">
-        <v>1.3283</v>
+        <v>-1.8279</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="X20" t="n">
-        <v>1.3283</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484323_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. MONTAGUT PUNTI</t>
+          <t>H. LOUASSA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.4758</v>
+        <v>2.3169</v>
       </c>
       <c r="E21" t="n">
-        <v>0.796</v>
+        <v>0.0235</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6798999999999999</v>
+        <v>2.2934</v>
       </c>
       <c r="G21" t="n">
-        <v>2.6259</v>
+        <v>-0.2068</v>
       </c>
       <c r="H21" t="n">
-        <v>1.4915</v>
+        <v>2.0044</v>
       </c>
       <c r="I21" t="n">
-        <v>1.1344</v>
+        <v>-2.2112</v>
       </c>
       <c r="J21" t="n">
-        <v>3.6036</v>
+        <v>0.0029</v>
       </c>
       <c r="K21" t="n">
-        <v>3.0085</v>
+        <v>1.9442</v>
       </c>
       <c r="L21" t="n">
-        <v>0.5951</v>
+        <v>-1.9414</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9777</v>
+        <v>-0.2097</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.517</v>
+        <v>0.0601</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5393</v>
+        <v>-0.2698</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5627</v>
+        <v>1.1721</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2174</v>
+        <v>0.0234</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1225</v>
+        <v>0.0207</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0949</v>
+        <v>0.0027</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.3283</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.3283</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484323_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G. ALBA ASTOLA</t>
+          <t>P. MONÉS RIERA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1333</v>
+        <v>1.521</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.3627</v>
+        <v>1.521</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2294</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8249</v>
+        <v>1.521</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6897</v>
+        <v>0.307</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1352</v>
+        <v>1.214</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2261</v>
+        <v>1.521</v>
       </c>
       <c r="K22" t="n">
-        <v>0.2251</v>
+        <v>0.307</v>
       </c>
       <c r="L22" t="n">
-        <v>0.001</v>
+        <v>1.214</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5988</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0.4646</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1342</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4911</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3646</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1265</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484323_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. MONTAGUT PUNTI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,68 +2309,318 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>35.7969</v>
+        <v>1.4758</v>
       </c>
       <c r="E23" t="n">
-        <v>25.7311</v>
+        <v>0.796</v>
       </c>
       <c r="F23" t="n">
+        <v>0.6798999999999999</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2.6259</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.4915</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.1344</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.6036</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.0085</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.5951</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-0.9777</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-1.517</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.5393</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-1.3674</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.5627</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.2174</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.1225</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.0949</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484323_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>P. MONES RIERA</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CB NAVÀS VISCOLA</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.9058</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2.2958</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-1.39</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.0644</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-2.4835</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3.548</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.2468</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-0.8967000000000001</v>
+      </c>
+      <c r="L24" t="n">
+        <v>3.1435</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-1.1824</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-1.5868</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.4045</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.2786</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.0489</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.2297</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484323_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>G. ALBA ASTOLA</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CB NAVÀS VISCOLA</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-0.1333</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-1.3627</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.2294</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.8249</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.6897</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.1352</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.2261</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.2251</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.5988</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.4646</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.1342</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.4911</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.3646</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.1265</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484323_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CB NAVÀS VISCOLA</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>35.797</v>
+      </c>
+      <c r="E26" t="n">
+        <v>25.7312</v>
+      </c>
+      <c r="F26" t="n">
         <v>10.0659</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G26" t="n">
         <v>28.3706</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H26" t="n">
         <v>13.5308</v>
       </c>
-      <c r="I23" t="n">
-        <v>14.8399</v>
-      </c>
-      <c r="J23" t="n">
+      <c r="I26" t="n">
+        <v>14.84</v>
+      </c>
+      <c r="J26" t="n">
         <v>30.9879</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K26" t="n">
         <v>18.8411</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L26" t="n">
         <v>12.1467</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M26" t="n">
         <v>-2.6173</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N26" t="n">
         <v>-5.3106</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O26" t="n">
         <v>2.6935</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P26" t="n">
         <v>-1.9535</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q26" t="n">
         <v>-14.6505</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R26" t="n">
         <v>12.6972</v>
       </c>
-      <c r="S23" t="n">
-        <v>7.4423</v>
-      </c>
-      <c r="T23" t="n">
+      <c r="S26" t="n">
+        <v>7.442300000000001</v>
+      </c>
+      <c r="T26" t="n">
         <v>3.6877</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U26" t="n">
         <v>3.7547</v>
       </c>
-      <c r="V23" t="n">
+      <c r="V26" t="n">
         <v>1.9377</v>
       </c>
-      <c r="W23" t="n">
+      <c r="W26" t="n">
         <v>5.7062</v>
       </c>
-      <c r="X23" t="n">
+      <c r="X26" t="n">
         <v>-3.7685</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
